--- a/data/trans_camb/P26-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P26-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 10,29</t>
+          <t>-3,29; 10,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,5; -2,2</t>
+          <t>-15,74; -1,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-36,63; -19,93</t>
+          <t>-37,41; -19,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 11,85</t>
+          <t>-1,56; 11,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-16,94; -3,54</t>
+          <t>-17,17; -3,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-32,69; -17,51</t>
+          <t>-33,14; -17,12</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 8,95</t>
+          <t>-0,24; 8,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-14,38; -4,86</t>
+          <t>-13,84; -4,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-32,67; -20,82</t>
+          <t>-32,6; -20,94</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 22,59</t>
+          <t>-6,44; 22,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-29,56; -4,8</t>
+          <t>-29,93; -3,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-72,19; -42,86</t>
+          <t>-74,5; -40,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 27,65</t>
+          <t>-3,05; 25,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-34,06; -7,82</t>
+          <t>-34,16; -8,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-67,02; -39,09</t>
+          <t>-67,33; -37,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 19,58</t>
+          <t>-0,5; 19,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-29,0; -10,93</t>
+          <t>-27,89; -10,55</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-66,04; -43,89</t>
+          <t>-65,92; -44,98</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 10,61</t>
+          <t>-0,03; 10,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,83; 2,94</t>
+          <t>-8,23; 1,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-22,93; -10,02</t>
+          <t>-22,71; -10,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 5,11</t>
+          <t>-6,28; 5,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,19; 0,41</t>
+          <t>-11,04; 0,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-31,62; -17,87</t>
+          <t>-32,69; -18,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 6,2</t>
+          <t>-1,32; 6,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,58; -0,07</t>
+          <t>-7,84; 0,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-25,44; -16,01</t>
+          <t>-25,2; -15,67</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 34,32</t>
+          <t>-0,29; 32,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-21,93; 9,36</t>
+          <t>-22,86; 6,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-65,02; -32,48</t>
+          <t>-64,25; -33,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,15; 13,81</t>
+          <t>-14,36; 14,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-25,65; 1,03</t>
+          <t>-25,47; 0,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-74,06; -46,22</t>
+          <t>-76,03; -47,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 17,85</t>
+          <t>-3,45; 18,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-19,86; -0,32</t>
+          <t>-20,44; 0,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-66,72; -45,36</t>
+          <t>-66,39; -44,1</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,14; 13,38</t>
+          <t>3,28; 12,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 6,7</t>
+          <t>-3,38; 6,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-18,18; -9,59</t>
+          <t>-18,41; -9,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 6,09</t>
+          <t>-5,33; 5,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-17,48; -7,08</t>
+          <t>-17,63; -7,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-30,15; -20,66</t>
+          <t>-30,46; -20,81</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,1; 7,87</t>
+          <t>-0,13; 7,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,01; -2,26</t>
+          <t>-9,27; -1,71</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-23,18; -16,91</t>
+          <t>-23,32; -16,97</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12,64; 65,54</t>
+          <t>12,4; 63,21</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-11,37; 32,33</t>
+          <t>-13,49; 32,34</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-71,62; -43,89</t>
+          <t>-72,44; -45,68</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-12,91; 16,75</t>
+          <t>-12,75; 15,15</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-41,34; -19,36</t>
+          <t>-41,74; -19,61</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-71,1; -56,16</t>
+          <t>-71,34; -56,69</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,04; 26,22</t>
+          <t>-0,36; 25,25</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-27,18; -8,12</t>
+          <t>-27,41; -5,65</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-69,27; -56,47</t>
+          <t>-69,85; -56,45</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 9,69</t>
+          <t>-2,32; 9,47</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,09; 0,42</t>
+          <t>-11,64; 0,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-20,69; 44,43</t>
+          <t>-20,67; 43,2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 10,68</t>
+          <t>-1,71; 11,17</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-20,1; -8,01</t>
+          <t>-19,93; -7,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-34,26; -24,24</t>
+          <t>-34,01; -23,5</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 8,31</t>
+          <t>-0,83; 8,08</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-13,87; -5,44</t>
+          <t>-13,76; -5,56</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-24,82; 20,66</t>
+          <t>-24,78; 24,04</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 36,15</t>
+          <t>-6,9; 35,29</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-33,51; 2,21</t>
+          <t>-34,52; 0,92</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-66,36; 163,71</t>
+          <t>-67,09; 154,02</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 27,13</t>
+          <t>-3,82; 28,56</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-42,83; -19,72</t>
+          <t>-43,34; -19,51</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-74,23; -60,73</t>
+          <t>-74,15; -60,76</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 24,77</t>
+          <t>-2,22; 23,38</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-35,42; -15,7</t>
+          <t>-35,54; -16,17</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-66,97; 58,81</t>
+          <t>-67,12; 67,84</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 10,48</t>
+          <t>-2,43; 11,02</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 6,92</t>
+          <t>-4,44; 7,13</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-14,84; -4,4</t>
+          <t>-14,35; -4,6</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 10,71</t>
+          <t>-3,07; 10,92</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-14,23; -1,43</t>
+          <t>-14,06; -1,24</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-24,43; -13,71</t>
+          <t>-24,99; -13,92</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 9,05</t>
+          <t>-0,23; 9,26</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-7,62; 1,19</t>
+          <t>-7,75; 1,15</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-18,03; -10,8</t>
+          <t>-18,19; -10,54</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 55,69</t>
+          <t>-9,73; 57,58</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-18,9; 35,74</t>
+          <t>-17,36; 38,06</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-58,49; -23,85</t>
+          <t>-56,41; -23,33</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-8,3; 37,33</t>
+          <t>-8,17; 37,78</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-39,49; -4,8</t>
+          <t>-39,16; -3,88</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-67,06; -48,26</t>
+          <t>-67,86; -48,27</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 36,16</t>
+          <t>-0,99; 36,25</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-25,65; 4,66</t>
+          <t>-25,67; 4,92</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-60,71; -43,9</t>
+          <t>-60,67; -42,89</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2,74; 14,63</t>
+          <t>2,78; 13,85</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 7,48</t>
+          <t>-2,34; 8,34</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 1,06</t>
+          <t>-7,36; 0,98</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 11,18</t>
+          <t>-1,69; 11,43</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-11,27; 0,24</t>
+          <t>-11,61; 0,62</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-20,43; -7,4</t>
+          <t>-21,0; -7,19</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,92; 11,13</t>
+          <t>1,88; 11,11</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 2,43</t>
+          <t>-5,61; 2,26</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-12,95; -4,84</t>
+          <t>-13,0; -4,76</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>17,99; 191,49</t>
+          <t>23,15; 209,96</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-22,86; 100,91</t>
+          <t>-19,97; 119,93</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-57,45; 19,44</t>
+          <t>-58,92; 13,69</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-10,56; 69,24</t>
+          <t>-9,72; 70,96</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-49,99; 2,2</t>
+          <t>-51,91; 2,93</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-90,55; -41,83</t>
+          <t>-88,74; -41,73</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>9,99; 87,41</t>
+          <t>10,5; 88,86</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-33,18; 20,46</t>
+          <t>-33,16; 17,95</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-78,26; -37,21</t>
+          <t>-79,23; -37,05</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 6,21</t>
+          <t>-7,04; 6,32</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-10,59; 1,22</t>
+          <t>-10,68; 1,3</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-15,84; -5,0</t>
+          <t>-15,55; -4,68</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 7,88</t>
+          <t>-5,87; 7,07</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-13,51; -0,3</t>
+          <t>-13,8; -0,59</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-17,88; -6,46</t>
+          <t>-17,36; -6,18</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 5,6</t>
+          <t>-5,22; 4,69</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-10,1; -1,82</t>
+          <t>-11,1; -1,68</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-14,82; -6,83</t>
+          <t>-15,24; -7,25</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-50,66; 87,59</t>
+          <t>-50,58; 85,02</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-68,53; 19,13</t>
+          <t>-68,99; 26,53</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-97,07; -67,39</t>
+          <t>-96,76; -62,95</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-27,8; 60,66</t>
+          <t>-28,56; 52,76</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-63,62; -1,82</t>
+          <t>-63,42; -1,24</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-78,89; -47,66</t>
+          <t>-77,99; -45,27</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-27,3; 49,4</t>
+          <t>-28,77; 38,87</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-56,59; -13,42</t>
+          <t>-60,37; -12,69</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-82,0; -58,5</t>
+          <t>-82,28; -60,7</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>2,08; 6,67</t>
+          <t>1,84; 6,53</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-5,71; -0,96</t>
+          <t>-5,73; -1,16</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-17,35; 10,12</t>
+          <t>-17,5; 7,46</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 4,14</t>
+          <t>-0,96; 4,22</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-12,79; -8,17</t>
+          <t>-12,63; -7,91</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-26,88; -21,91</t>
+          <t>-27,27; -21,99</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,28; 4,59</t>
+          <t>1,25; 4,77</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-8,53; -5,36</t>
+          <t>-8,51; -5,23</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-21,01; -6,08</t>
+          <t>-21,23; -6,26</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>6,98; 24,33</t>
+          <t>6,17; 23,85</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-19,11; -3,51</t>
+          <t>-19,14; -4,44</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-59,93; 35,66</t>
+          <t>-60,93; 25,05</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 11,53</t>
+          <t>-2,52; 11,97</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-33,19; -22,59</t>
+          <t>-32,98; -22,4</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-71,9; -61,01</t>
+          <t>-72,0; -60,76</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,78; 14,43</t>
+          <t>3,62; 14,87</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-25,33; -16,61</t>
+          <t>-25,31; -16,4</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-63,74; -18,62</t>
+          <t>-63,98; -19,64</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P26-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P26-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-28,71</t>
+          <t>-29,04</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-25,51</t>
+          <t>-27,11</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-27,23</t>
+          <t>-28,1</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 10,07</t>
+          <t>-3,4; 10,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,74; -1,76</t>
+          <t>-14,99; -1,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-37,41; -19,37</t>
+          <t>-36,6; -19,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 11,21</t>
+          <t>-1,96; 11,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-17,17; -3,76</t>
+          <t>-17,02; -3,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-33,14; -17,12</t>
+          <t>-34,0; -19,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 8,84</t>
+          <t>-0,23; 9,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-13,84; -4,71</t>
+          <t>-14,06; -4,95</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-32,6; -20,94</t>
+          <t>-33,18; -22,11</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-59,01%</t>
+          <t>-59,7%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-54,2%</t>
+          <t>-57,61%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-56,88%</t>
+          <t>-58,71%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,44; 22,01</t>
+          <t>-6,43; 23,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-29,93; -3,81</t>
+          <t>-29,48; -3,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-74,5; -40,97</t>
+          <t>-72,47; -42,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 25,83</t>
+          <t>-3,82; 26,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-34,16; -8,5</t>
+          <t>-35,13; -8,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-67,33; -37,93</t>
+          <t>-68,89; -42,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 19,77</t>
+          <t>-0,49; 19,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-27,89; -10,55</t>
+          <t>-28,49; -10,83</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-65,92; -44,98</t>
+          <t>-68,44; -48,42</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-16,98</t>
+          <t>-16,56</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-24,18</t>
+          <t>-23,77</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-20,3</t>
+          <t>-19,89</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 10,27</t>
+          <t>-0,05; 10,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 1,98</t>
+          <t>-7,75; 2,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-22,71; -10,62</t>
+          <t>-22,42; -10,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 5,44</t>
+          <t>-6,23; 5,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,04; 0,01</t>
+          <t>-10,69; 0,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-32,69; -18,56</t>
+          <t>-29,32; -18,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 6,32</t>
+          <t>-1,3; 6,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 0,16</t>
+          <t>-7,65; 0,21</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-25,2; -15,67</t>
+          <t>-23,8; -15,45</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-50,52%</t>
+          <t>-49,26%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-59,22%</t>
+          <t>-58,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-54,96%</t>
+          <t>-53,84%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 32,88</t>
+          <t>-0,06; 34,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-22,86; 6,58</t>
+          <t>-21,64; 9,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-64,25; -33,04</t>
+          <t>-64,56; -31,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,36; 14,11</t>
+          <t>-14,53; 13,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-25,47; 0,04</t>
+          <t>-24,72; 1,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-76,03; -47,16</t>
+          <t>-67,51; -48,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 18,25</t>
+          <t>-3,2; 17,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-20,44; 0,35</t>
+          <t>-19,98; 0,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-66,39; -44,1</t>
+          <t>-61,71; -43,94</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-14,05</t>
+          <t>-14,63</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-25,53</t>
+          <t>-25,65</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-20,14</t>
+          <t>-20,48</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,28; 12,94</t>
+          <t>2,88; 12,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 6,66</t>
+          <t>-3,2; 6,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-18,41; -9,65</t>
+          <t>-19,15; -10,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 5,61</t>
+          <t>-5,25; 5,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-17,63; -7,44</t>
+          <t>-17,03; -7,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-30,46; -20,81</t>
+          <t>-30,41; -21,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 7,53</t>
+          <t>-0,24; 7,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,27; -1,71</t>
+          <t>-9,71; -2,3</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-23,32; -16,97</t>
+          <t>-23,46; -17,01</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-60,67%</t>
+          <t>-63,17%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-64,45%</t>
+          <t>-64,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-63,33%</t>
+          <t>-64,4%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12,4; 63,21</t>
+          <t>10,42; 62,74</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-13,49; 32,34</t>
+          <t>-13,01; 33,36</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-72,44; -45,68</t>
+          <t>-73,23; -48,6</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-12,75; 15,15</t>
+          <t>-12,42; 13,76</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-41,74; -19,61</t>
+          <t>-41,31; -19,83</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-71,34; -56,69</t>
+          <t>-71,78; -57,75</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 25,25</t>
+          <t>-0,53; 26,09</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-27,41; -5,65</t>
+          <t>-28,92; -8,03</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-69,85; -56,45</t>
+          <t>-70,02; -57,42</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7,76</t>
+          <t>-18,78</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-29,15</t>
+          <t>-28,45</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-9,7</t>
+          <t>-23,49</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 9,47</t>
+          <t>-2,55; 9,41</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,64; 0,11</t>
+          <t>-11,87; 0,22</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-20,67; 43,2</t>
+          <t>-23,63; -13,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 11,17</t>
+          <t>-1,73; 10,41</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-19,93; -7,69</t>
+          <t>-19,76; -8,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-34,01; -23,5</t>
+          <t>-33,54; -23,44</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 8,08</t>
+          <t>-0,41; 8,57</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-13,76; -5,56</t>
+          <t>-13,71; -5,29</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-24,78; 24,04</t>
+          <t>-26,91; -19,81</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>-62,42%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-67,96%</t>
+          <t>-66,33%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-26,6%</t>
+          <t>-64,39%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-6,9; 35,29</t>
+          <t>-7,52; 34,83</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-34,52; 0,92</t>
+          <t>-35,24; 0,47</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-67,09; 154,02</t>
+          <t>-71,32; -48,86</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 28,56</t>
+          <t>-3,71; 25,64</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-43,34; -19,51</t>
+          <t>-43,04; -20,7</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-74,15; -60,76</t>
+          <t>-71,98; -59,83</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 23,38</t>
+          <t>-1,05; 25,22</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-35,54; -16,17</t>
+          <t>-35,69; -14,61</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-67,12; 67,84</t>
+          <t>-69,37; -58,94</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-9,23</t>
+          <t>-9,6</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-19,37</t>
+          <t>-19,71</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-14,39</t>
+          <t>-14,74</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 11,02</t>
+          <t>-1,77; 10,59</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 7,13</t>
+          <t>-5,32; 6,89</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-14,35; -4,6</t>
+          <t>-15,59; -5,45</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 10,92</t>
+          <t>-3,09; 11,45</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-14,06; -1,24</t>
+          <t>-14,2; -1,12</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-24,99; -13,92</t>
+          <t>-25,1; -14,18</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 9,26</t>
+          <t>-0,24; 9,11</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 1,15</t>
+          <t>-7,57; 1,55</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-18,19; -10,54</t>
+          <t>-18,39; -11,1</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-42,09%</t>
+          <t>-43,79%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-59,47%</t>
+          <t>-60,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-52,65%</t>
+          <t>-53,94%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-9,73; 57,58</t>
+          <t>-7,01; 56,96</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-17,36; 38,06</t>
+          <t>-20,9; 37,42</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-56,41; -23,33</t>
+          <t>-60,42; -27,17</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 37,78</t>
+          <t>-8,78; 40,42</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-39,16; -3,88</t>
+          <t>-39,67; -3,89</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-67,86; -48,27</t>
+          <t>-68,56; -49,12</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 36,25</t>
+          <t>-0,87; 37,36</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-25,67; 4,92</t>
+          <t>-25,86; 5,94</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-60,67; -42,89</t>
+          <t>-61,45; -44,67</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-2,9</t>
+          <t>-2,93</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-13,2</t>
+          <t>-9,37</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-8,28</t>
+          <t>-6,28</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2,78; 13,85</t>
+          <t>3,01; 14,63</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 8,34</t>
+          <t>-1,9; 8,82</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-7,36; 0,98</t>
+          <t>-7,23; 1,21</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 11,43</t>
+          <t>-1,98; 10,86</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-11,61; 0,62</t>
+          <t>-11,47; -0,04</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-21,0; -7,19</t>
+          <t>-14,51; -4,86</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,88; 11,11</t>
+          <t>1,76; 11,2</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 2,26</t>
+          <t>-5,12; 2,31</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-13,0; -4,76</t>
+          <t>-9,54; -3,27</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-30,06%</t>
+          <t>-30,38%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-68,56%</t>
+          <t>-48,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-56,74%</t>
+          <t>-43,07%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>23,15; 209,96</t>
+          <t>22,91; 201,86</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-19,97; 119,93</t>
+          <t>-14,98; 124,97</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-58,92; 13,69</t>
+          <t>-57,57; 19,44</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-9,72; 70,96</t>
+          <t>-9,38; 69,63</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-51,91; 2,93</t>
+          <t>-51,39; -0,04</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-88,74; -41,73</t>
+          <t>-63,37; -29,39</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>10,5; 88,86</t>
+          <t>10,62; 89,56</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-33,16; 17,95</t>
+          <t>-31,31; 18,36</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-79,23; -37,05</t>
+          <t>-56,29; -24,93</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-9,61</t>
+          <t>-9,56</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-11,48</t>
+          <t>-11,26</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-10,78</t>
+          <t>-10,65</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 6,32</t>
+          <t>-7,74; 6,66</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-10,68; 1,3</t>
+          <t>-10,64; 1,41</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-15,55; -4,68</t>
+          <t>-15,82; -5,12</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 7,07</t>
+          <t>-6,38; 7,14</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-13,8; -0,59</t>
+          <t>-13,46; -0,76</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-17,36; -6,18</t>
+          <t>-17,01; -6,29</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 4,69</t>
+          <t>-4,65; 4,91</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-11,1; -1,68</t>
+          <t>-10,6; -1,56</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-15,24; -7,25</t>
+          <t>-14,55; -6,63</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-87,5%</t>
+          <t>-87,03%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-65,86%</t>
+          <t>-64,65%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-73,08%</t>
+          <t>-72,18%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-50,58; 85,02</t>
+          <t>-51,7; 96,41</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-68,99; 26,53</t>
+          <t>-68,68; 21,7</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-96,76; -62,95</t>
+          <t>-96,1; -65,07</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-28,56; 52,76</t>
+          <t>-30,78; 49,66</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-63,42; -1,24</t>
+          <t>-63,65; -2,12</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-77,99; -45,27</t>
+          <t>-77,23; -43,99</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-28,77; 38,87</t>
+          <t>-26,27; 40,02</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-60,37; -12,69</t>
+          <t>-60,03; -12,11</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-82,28; -60,7</t>
+          <t>-81,55; -56,84</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-10,14</t>
+          <t>-17,18</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-24,21</t>
+          <t>-23,37</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-17,28</t>
+          <t>-20,27</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>1,84; 6,53</t>
+          <t>1,96; 6,52</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-5,73; -1,16</t>
+          <t>-5,51; -1,01</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-17,5; 7,46</t>
+          <t>-19,49; -15,0</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 4,22</t>
+          <t>-1,06; 3,97</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-12,63; -7,91</t>
+          <t>-12,87; -8,28</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-27,27; -21,99</t>
+          <t>-25,49; -21,35</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,25; 4,77</t>
+          <t>1,24; 4,56</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-8,51; -5,23</t>
+          <t>-8,42; -5,07</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-21,23; -6,26</t>
+          <t>-21,65; -18,66</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-35,41%</t>
+          <t>-60,0%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-65,27%</t>
+          <t>-63,02%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-52,56%</t>
+          <t>-61,63%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>6,17; 23,85</t>
+          <t>6,5; 23,36</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-19,14; -4,44</t>
+          <t>-18,62; -3,71</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-60,93; 25,05</t>
+          <t>-65,17; -54,15</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 11,97</t>
+          <t>-2,72; 10,95</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-32,98; -22,4</t>
+          <t>-33,48; -22,9</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-72,0; -60,76</t>
+          <t>-66,3; -59,52</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,62; 14,87</t>
+          <t>3,76; 14,33</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-25,31; -16,4</t>
+          <t>-25,02; -15,89</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-63,98; -19,64</t>
+          <t>-64,36; -58,43</t>
         </is>
       </c>
     </row>
